--- a/phase2/法诉案件导入_批次处理明细.xlsx
+++ b/phase2/法诉案件导入_批次处理明细.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="R8c20f429ee754c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="Rc39b342c78974c06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="R663af617a6c64c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="R2e49cc64af684a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="R423cbb02622d4e64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="Rce3ddc8f3d694385"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,13 +433,13 @@
         <x:v>缺少必填材料</x:v>
       </x:c>
       <x:c r="I3" s="8" t="str">
-        <x:v>待补材料</x:v>
+        <x:v>待材料补齐</x:v>
       </x:c>
       <x:c r="J3" s="8" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
       <x:c r="K3" s="8" t="str">
-        <x:v>待补必填材料</x:v>
+        <x:v>待补必填</x:v>
       </x:c>
       <x:c r="L3" s="8" t="str"/>
       <x:c r="M3" s="8" t="str">
@@ -482,7 +482,7 @@
         <x:v>已生效</x:v>
       </x:c>
       <x:c r="K4" s="8" t="str">
-        <x:v>材料待补</x:v>
+        <x:v>待补非必填</x:v>
       </x:c>
       <x:c r="L4" s="8" t="str"/>
       <x:c r="M4" s="8" t="str">
@@ -693,7 +693,7 @@
       </x:c>
       <x:c r="H3" s="8" t="str"/>
       <x:c r="I3" s="8" t="str">
-        <x:v>待补传</x:v>
+        <x:v>待补必填</x:v>
       </x:c>
       <x:c r="J3" s="8" t="str">
         <x:v>未匹配到必填材料</x:v>
@@ -726,7 +726,7 @@
       </x:c>
       <x:c r="H4" s="8" t="str"/>
       <x:c r="I4" s="8" t="str">
-        <x:v>材料待补</x:v>
+        <x:v>待补非必填</x:v>
       </x:c>
       <x:c r="J4" s="8" t="str">
         <x:v>未匹配到非必填材料</x:v>
@@ -817,7 +817,7 @@
         <x:v>2026-06-10 20:15:48</x:v>
       </x:c>
       <x:c r="E2" s="8" t="str">
-        <x:v>待处理</x:v>
+        <x:v>待重传</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="36" customHeight="1">
